--- a/data/estado.xlsx
+++ b/data/estado.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="145">
   <si>
     <t xml:space="preserve">EL LABORATORIO SECRETO — Registro maestro de misiones</t>
   </si>
@@ -81,6 +81,27 @@
     <t xml:space="preserve">Pendiente</t>
   </si>
   <si>
+    <t xml:space="preserve">03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El mapa de los electrones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exploracion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El primer parpadeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tres colores</t>
+  </si>
+  <si>
     <t xml:space="preserve">06</t>
   </si>
   <si>
@@ -97,6 +118,264 @@
   </si>
   <si>
     <t xml:space="preserve">Ruta B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El codigo secreto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La resistencia invisible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dos luces, una mision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El semaforo secreto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El boton maestro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El potenciometro magico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controla la intensidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La alarma del laboratorio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El sonido que avisa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El rele misterioso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El codigo de colores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La feria de luces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El laboratorio tiene fiebre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Que tan humedo esta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El sensor que ve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La luz fantasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El detector de obstaculos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hay alguien ahi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El oido electronico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La pantalla secreta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El laboratorio habla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El mapa de sensores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El codigo secreto del sensor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El guardian de temperatura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La maquina de decisiones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si pasa esto...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La puerta secreta 2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alarma de intrusos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El detector de luz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El motor cobra vida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Especial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La maquina automatica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El circuito misterioso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La fabrica de piezas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El reto de los tres componentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La maquina de reaccion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El desafio de los sensores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La maquina inutil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El invento imposible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secreta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El gran proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El laboratorio es tuyo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final secreto</t>
   </si>
   <si>
     <t xml:space="preserve">Para agregar una misión nueva: copia una fila, pon su ID y deja Estado = Pendiente.</t>
@@ -610,7 +889,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -722,16 +1001,16 @@
         <v>20</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>18</v>
@@ -746,25 +1025,1057 @@
         <v>23</v>
       </c>
       <c r="C9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="4" t="n">
+      <c r="D16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F16" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="G16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F17" s="4" t="n">
         <v>25</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="5"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="5"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" s="5"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="5"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" s="5"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34" s="5"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" s="5"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37" s="5"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="5"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H39" s="5"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H40" s="5"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41" s="5"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H42" s="5"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H43" s="5"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" s="5"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" s="5"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" s="5"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H47" s="5"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48" s="5"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H49" s="5"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H50" s="5"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H51" s="5"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H52" s="5"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -794,48 +2105,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>29</v>
+        <v>122</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>30</v>
+        <v>123</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>32</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>33</v>
+        <v>126</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>34</v>
+        <v>127</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>35</v>
+        <v>128</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>10</v>
@@ -844,13 +2155,13 @@
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>38</v>
+        <v>131</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>39</v>
+        <v>132</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>0</v>
@@ -859,13 +2170,13 @@
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
       <c r="B8" s="5" t="s">
-        <v>40</v>
+        <v>133</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>42</v>
+        <v>135</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>0</v>
@@ -874,13 +2185,13 @@
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
       <c r="B9" s="5" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>45</v>
+        <v>138</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>0</v>
@@ -911,35 +2222,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>47</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="B4" s="7" t="n">
-        <f aca="false">SUMIFS(Misiones!F6:F9,Misiones!G6:G9,"Completada")</f>
+        <f aca="false">SUMIFS(Misiones!F6:F52,Misiones!G6:G52,"Completada")</f>
         <v>20</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="B5" s="7" t="n">
-        <f aca="false">SUMIFS(Misiones!E6:E9,Misiones!G6:G9,"Completada")</f>
+        <f aca="false">SUMIFS(Misiones!E6:E52,Misiones!G6:G52,"Completada")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="B6" s="7" t="n">
         <f aca="false">SUM(Canjes!E6:E35)</f>
@@ -948,7 +2259,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>51</v>
+        <v>144</v>
       </c>
       <c r="B7" s="7" t="n">
         <f aca="false">B4-B5-B6</f>

--- a/data/estado.xlsx
+++ b/data/estado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/JM/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_13430C1536595A58853DAEB0D8416F49BBD76EEC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB9BB3A5-11B8-4E3C-A91D-92F7EBBFE807}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_13430C1536595A58853DAEB0D8416F49BBD76EEC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D08FA57D-74E1-42A4-9ACD-B16FF6A2D7CB}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1296" yWindow="3444" windowWidth="17256" windowHeight="8856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Misiones" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="144">
   <si>
     <t>EL LABORATORIO SECRETO — Registro maestro de misiones</t>
   </si>
@@ -80,6 +80,9 @@
   </si>
   <si>
     <t>Principal</t>
+  </si>
+  <si>
+    <t>Completada</t>
   </si>
   <si>
     <t>02</t>
@@ -917,16 +920,16 @@
         <v>20</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
@@ -941,22 +944,22 @@
         <v>20</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="4">
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" s="4">
         <v>15</v>
@@ -965,16 +968,16 @@
         <v>15</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="4">
         <v>1</v>
@@ -989,16 +992,16 @@
         <v>20</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="4">
         <v>1</v>
@@ -1013,22 +1016,22 @@
         <v>20</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="4">
         <v>1</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11" s="4">
         <v>20</v>
@@ -1037,22 +1040,22 @@
         <v>25</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" s="4">
         <v>1</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12" s="4">
         <v>20</v>
@@ -1061,16 +1064,16 @@
         <v>25</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" s="4">
         <v>1</v>
@@ -1085,22 +1088,22 @@
         <v>25</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" s="4">
         <v>1</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14" s="4">
         <v>0</v>
@@ -1109,16 +1112,16 @@
         <v>15</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C15" s="4">
         <v>1</v>
@@ -1133,16 +1136,16 @@
         <v>25</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" s="4">
         <v>2</v>
@@ -1157,16 +1160,16 @@
         <v>25</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" s="4">
         <v>2</v>
@@ -1181,16 +1184,16 @@
         <v>25</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C18" s="4">
         <v>2</v>
@@ -1205,22 +1208,22 @@
         <v>25</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" s="4">
         <v>2</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E19" s="4">
         <v>20</v>
@@ -1229,16 +1232,16 @@
         <v>30</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C20" s="4">
         <v>2</v>
@@ -1253,16 +1256,16 @@
         <v>25</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" s="4">
         <v>2</v>
@@ -1277,16 +1280,16 @@
         <v>30</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" s="4">
         <v>2</v>
@@ -1301,22 +1304,22 @@
         <v>30</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C23" s="4">
         <v>2</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E23" s="4">
         <v>0</v>
@@ -1325,22 +1328,22 @@
         <v>15</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C24" s="4">
         <v>2</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E24" s="4">
         <v>25</v>
@@ -1349,16 +1352,16 @@
         <v>35</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C25" s="4">
         <v>3</v>
@@ -1373,16 +1376,16 @@
         <v>30</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C26" s="4">
         <v>3</v>
@@ -1397,16 +1400,16 @@
         <v>30</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C27" s="4">
         <v>3</v>
@@ -1421,22 +1424,22 @@
         <v>30</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C28" s="4">
         <v>3</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E28" s="4">
         <v>25</v>
@@ -1445,16 +1448,16 @@
         <v>35</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H28" s="5"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C29" s="4">
         <v>3</v>
@@ -1469,22 +1472,22 @@
         <v>30</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H29" s="5"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C30" s="4">
         <v>3</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E30" s="4">
         <v>30</v>
@@ -1493,22 +1496,22 @@
         <v>35</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H30" s="5"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C31" s="4">
         <v>3</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E31" s="4">
         <v>30</v>
@@ -1517,16 +1520,16 @@
         <v>35</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H31" s="5"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C32" s="4">
         <v>3</v>
@@ -1541,22 +1544,22 @@
         <v>35</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H32" s="5"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C33" s="4">
         <v>3</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E33" s="4">
         <v>30</v>
@@ -1565,22 +1568,22 @@
         <v>35</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H33" s="5"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C34" s="4">
         <v>3</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E34" s="4">
         <v>0</v>
@@ -1589,22 +1592,22 @@
         <v>20</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H34" s="5"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C35" s="4">
         <v>3</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E35" s="4">
         <v>0</v>
@@ -1613,16 +1616,16 @@
         <v>20</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H35" s="5"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C36" s="4">
         <v>4</v>
@@ -1637,16 +1640,16 @@
         <v>35</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H36" s="5"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C37" s="4">
         <v>4</v>
@@ -1661,16 +1664,16 @@
         <v>35</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H37" s="5"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C38" s="4">
         <v>4</v>
@@ -1685,22 +1688,22 @@
         <v>35</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H38" s="5"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C39" s="4">
         <v>4</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E39" s="4">
         <v>30</v>
@@ -1709,22 +1712,22 @@
         <v>35</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H39" s="5"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C40" s="4">
         <v>4</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E40" s="4">
         <v>30</v>
@@ -1733,16 +1736,16 @@
         <v>35</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H40" s="5"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C41" s="4">
         <v>4</v>
@@ -1757,22 +1760,22 @@
         <v>35</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H41" s="5"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C42" s="4">
         <v>4</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E42" s="4">
         <v>40</v>
@@ -1781,16 +1784,16 @@
         <v>45</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H42" s="5"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C43" s="4">
         <v>4</v>
@@ -1805,22 +1808,22 @@
         <v>35</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H43" s="5"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C44" s="4">
         <v>4</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E44" s="4">
         <v>35</v>
@@ -1829,22 +1832,22 @@
         <v>40</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H44" s="5"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C45" s="4">
         <v>4</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E45" s="4">
         <v>0</v>
@@ -1853,22 +1856,22 @@
         <v>20</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H45" s="5"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C46" s="4">
         <v>5</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E46" s="4">
         <v>35</v>
@@ -1877,22 +1880,22 @@
         <v>40</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H46" s="5"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C47" s="4">
         <v>5</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E47" s="4">
         <v>35</v>
@@ -1901,22 +1904,22 @@
         <v>40</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H47" s="5"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C48" s="4">
         <v>5</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E48" s="4">
         <v>35</v>
@@ -1925,22 +1928,22 @@
         <v>40</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H48" s="5"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C49" s="4">
         <v>5</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E49" s="4">
         <v>0</v>
@@ -1949,22 +1952,22 @@
         <v>20</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H49" s="5"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C50" s="4">
         <v>5</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E50" s="4">
         <v>0</v>
@@ -1973,22 +1976,22 @@
         <v>40</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H50" s="5"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C51" s="4">
         <v>5</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E51" s="4">
         <v>50</v>
@@ -1997,22 +2000,22 @@
         <v>60</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H51" s="5"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C52" s="4">
         <v>5</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E52" s="4">
         <v>0</v>
@@ -2021,13 +2024,13 @@
         <v>100</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H52" s="5"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2049,48 +2052,48 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E6" s="5">
         <v>0</v>
@@ -2099,13 +2102,13 @@
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E7" s="5">
         <v>0</v>
@@ -2114,13 +2117,13 @@
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E8" s="5">
         <v>0</v>
@@ -2129,13 +2132,13 @@
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E9" s="5">
         <v>0</v>
@@ -2158,35 +2161,35 @@
   <sheetData>
     <row r="1" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B4" s="7">
         <f>SUMIFS(Misiones!F6:F52,Misiones!G6:G52,"Completada")</f>
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B5" s="7">
         <f>SUMIFS(Misiones!E6:E52,Misiones!G6:G52,"Completada")</f>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B6" s="7">
         <f>SUM(Canjes!E6:E35)</f>
@@ -2195,11 +2198,11 @@
     </row>
     <row r="7" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B7" s="7">
         <f>B4-B5-B6</f>
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/data/estado.xlsx
+++ b/data/estado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/JM/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_13430C1536595A58853DAEB0D8416F49BBD76EEC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D08FA57D-74E1-42A4-9ACD-B16FF6A2D7CB}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_13430C1536595A58853DAEB0D8416F49BBD76EEC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{673DF415-2801-4E9C-98EB-8992FD7F76E6}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1296" yWindow="3444" windowWidth="17256" windowHeight="8856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Misiones" sheetId="1" r:id="rId1"/>
@@ -476,7 +476,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -516,6 +516,14 @@
       <color rgb="FF1F6F4A"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -571,7 +579,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -582,6 +590,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -846,7 +855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -859,22 +868,22 @@
     <col min="8" max="8" width="19.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -900,7 +909,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
@@ -923,8 +932,9 @@
         <v>14</v>
       </c>
       <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
@@ -948,7 +958,7 @@
       </c>
       <c r="H7" s="5"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
@@ -972,7 +982,7 @@
       </c>
       <c r="H8" s="5"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>21</v>
       </c>
@@ -996,7 +1006,7 @@
       </c>
       <c r="H9" s="5"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>23</v>
       </c>
@@ -1020,7 +1030,7 @@
       </c>
       <c r="H10" s="5"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>25</v>
       </c>
@@ -1044,7 +1054,7 @@
       </c>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>28</v>
       </c>
@@ -1068,7 +1078,7 @@
       </c>
       <c r="H12" s="5"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>31</v>
       </c>
@@ -1092,7 +1102,7 @@
       </c>
       <c r="H13" s="5"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>33</v>
       </c>
@@ -1116,7 +1126,7 @@
       </c>
       <c r="H14" s="5"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>36</v>
       </c>
@@ -1140,7 +1150,7 @@
       </c>
       <c r="H15" s="5"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>38</v>
       </c>
